--- a/data/performance/daily/signal_list_2026-06-30.xlsx
+++ b/data/performance/daily/signal_list_2026-06-30.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-06-30.xlsx
+++ b/data/performance/daily/signal_list_2026-06-30.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -461,9 +461,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -493,7 +494,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -518,15 +519,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -563,12 +569,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -605,12 +616,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -647,12 +663,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -689,12 +710,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -731,12 +757,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -773,12 +804,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -810,17 +846,22 @@
       <c r="G11" s="4" t="n">
         <v>-1.37</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -857,12 +898,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -899,12 +945,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -936,17 +987,22 @@
       <c r="G14" s="4" t="n">
         <v>-1.56</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -978,17 +1034,22 @@
       <c r="G15" s="4" t="n">
         <v>-4.08</v>
       </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1020,17 +1081,22 @@
       <c r="G16" s="4" t="n">
         <v>-4.1</v>
       </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1047,7 +1113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1057,9 +1123,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1089,7 +1156,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1114,15 +1181,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1159,12 +1231,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1201,12 +1278,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1243,12 +1325,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1285,12 +1372,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1322,17 +1414,22 @@
       <c r="G9" s="4" t="n">
         <v>-4.14</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1369,12 +1466,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1411,12 +1513,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1448,17 +1555,22 @@
       <c r="G12" s="4" t="n">
         <v>-0.68</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1495,12 +1607,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1537,12 +1654,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1579,12 +1701,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1616,17 +1743,22 @@
       <c r="G16" s="4" t="n">
         <v>-3.57</v>
       </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1658,17 +1790,22 @@
       <c r="G17" s="4" t="n">
         <v>-1.92</v>
       </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1700,17 +1837,22 @@
       <c r="G18" s="4" t="n">
         <v>-0.59</v>
       </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1747,12 +1889,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1789,12 +1936,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1831,12 +1983,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1868,17 +2025,22 @@
       <c r="G22" s="4" t="n">
         <v>-3.31</v>
       </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1910,17 +2072,22 @@
       <c r="G23" s="4" t="n">
         <v>-7.41</v>
       </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1952,17 +2119,22 @@
       <c r="G24" s="4" t="n">
         <v>-2.42</v>
       </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1994,17 +2166,22 @@
       <c r="G25" s="4" t="n">
         <v>-6.7</v>
       </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2041,12 +2218,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2083,12 +2265,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2120,17 +2307,22 @@
       <c r="G28" s="4" t="n">
         <v>-14.81</v>
       </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2167,12 +2359,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2209,12 +2406,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2251,12 +2453,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2293,12 +2500,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2335,12 +2547,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2377,12 +2594,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2414,17 +2636,22 @@
       <c r="G35" s="4" t="n">
         <v>-4.08</v>
       </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2456,17 +2683,22 @@
       <c r="G36" s="4" t="n">
         <v>-3.26</v>
       </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2498,17 +2730,22 @@
       <c r="G37" s="4" t="n">
         <v>-8.99</v>
       </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2540,17 +2777,22 @@
       <c r="G38" s="4" t="n">
         <v>-8.890000000000001</v>
       </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2582,17 +2824,22 @@
       <c r="G39" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2629,12 +2876,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2671,12 +2923,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2713,12 +2970,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>

--- a/data/performance/daily/signal_list_2026-06-30.xlsx
+++ b/data/performance/daily/signal_list_2026-06-30.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -459,12 +459,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,45 +495,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -553,33 +559,36 @@
         <v>125</v>
       </c>
       <c r="D5" t="n">
-        <v>113</v>
+        <v/>
       </c>
       <c r="E5" t="n">
         <v>113</v>
       </c>
-      <c r="F5" s="4" t="n">
-        <v>-9.6</v>
+      <c r="F5" t="n">
+        <v>113</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>-9.6</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+      <c r="H5" s="4" t="n">
+        <v>-9.6</v>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -600,33 +609,36 @@
         <v>125</v>
       </c>
       <c r="D6" t="n">
-        <v>113</v>
+        <v/>
       </c>
       <c r="E6" t="n">
         <v>113</v>
       </c>
-      <c r="F6" s="4" t="n">
-        <v>-9.6</v>
+      <c r="F6" t="n">
+        <v>113</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>-9.6</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+      <c r="H6" s="4" t="n">
+        <v>-9.6</v>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -647,33 +659,36 @@
         <v>125</v>
       </c>
       <c r="D7" t="n">
-        <v>113</v>
+        <v/>
       </c>
       <c r="E7" t="n">
         <v>113</v>
       </c>
-      <c r="F7" s="4" t="n">
-        <v>-9.6</v>
+      <c r="F7" t="n">
+        <v>113</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>-9.6</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+      <c r="H7" s="4" t="n">
+        <v>-9.6</v>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -694,33 +709,36 @@
         <v>125</v>
       </c>
       <c r="D8" t="n">
-        <v>113</v>
+        <v/>
       </c>
       <c r="E8" t="n">
         <v>113</v>
       </c>
-      <c r="F8" s="4" t="n">
-        <v>-9.6</v>
+      <c r="F8" t="n">
+        <v>113</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>-9.6</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+      <c r="H8" s="4" t="n">
+        <v>-9.6</v>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -741,33 +759,36 @@
         <v>3980</v>
       </c>
       <c r="D9" t="n">
+        <v/>
+      </c>
+      <c r="E9" t="n">
         <v>3960</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>3980</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>-0.5</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -788,33 +809,36 @@
         <v>328</v>
       </c>
       <c r="D10" t="n">
+        <v/>
+      </c>
+      <c r="E10" t="n">
         <v>320</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>328</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>-2.44</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -835,33 +859,36 @@
         <v>16475</v>
       </c>
       <c r="D11" t="n">
+        <v/>
+      </c>
+      <c r="E11" t="n">
         <v>16250</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>16500</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>0.15</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>-1.37</v>
       </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -882,33 +909,36 @@
         <v>1080</v>
       </c>
       <c r="D12" t="n">
-        <v>1080</v>
+        <v/>
       </c>
       <c r="E12" t="n">
         <v>1080</v>
       </c>
-      <c r="F12" s="4" t="n">
-        <v>0</v>
+      <c r="F12" t="n">
+        <v>1080</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+      <c r="H12" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -929,33 +959,36 @@
         <v>1510</v>
       </c>
       <c r="D13" t="n">
-        <v>1525</v>
+        <v/>
       </c>
       <c r="E13" t="n">
         <v>1525</v>
       </c>
-      <c r="F13" s="4" t="n">
-        <v>0.99</v>
+      <c r="F13" t="n">
+        <v>1525</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H13" s="4" t="n">
+        <v>0.99</v>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -976,33 +1009,36 @@
         <v>960</v>
       </c>
       <c r="D14" t="n">
+        <v/>
+      </c>
+      <c r="E14" t="n">
         <v>945</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>965</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>0.52</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>-1.56</v>
       </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1023,33 +1059,36 @@
         <v>98</v>
       </c>
       <c r="D15" t="n">
+        <v/>
+      </c>
+      <c r="E15" t="n">
         <v>94</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>100</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>2.04</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="H15" s="4" t="n">
         <v>-4.08</v>
       </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1070,33 +1109,36 @@
         <v>1220</v>
       </c>
       <c r="D16" t="n">
+        <v/>
+      </c>
+      <c r="E16" t="n">
         <v>1170</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>1225</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>0.41</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="H16" s="4" t="n">
         <v>-4.1</v>
       </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1113,7 +1155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1121,12 +1163,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1156,45 +1199,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1215,33 +1263,36 @@
         <v>125</v>
       </c>
       <c r="D5" t="n">
-        <v>113</v>
+        <v/>
       </c>
       <c r="E5" t="n">
         <v>113</v>
       </c>
-      <c r="F5" s="4" t="n">
-        <v>-9.6</v>
+      <c r="F5" t="n">
+        <v>113</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>-9.6</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+      <c r="H5" s="4" t="n">
+        <v>-9.6</v>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1262,33 +1313,36 @@
         <v>125</v>
       </c>
       <c r="D6" t="n">
-        <v>113</v>
+        <v/>
       </c>
       <c r="E6" t="n">
         <v>113</v>
       </c>
-      <c r="F6" s="4" t="n">
-        <v>-9.6</v>
+      <c r="F6" t="n">
+        <v>113</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>-9.6</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+      <c r="H6" s="4" t="n">
+        <v>-9.6</v>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1309,33 +1363,36 @@
         <v>125</v>
       </c>
       <c r="D7" t="n">
-        <v>113</v>
+        <v/>
       </c>
       <c r="E7" t="n">
         <v>113</v>
       </c>
-      <c r="F7" s="4" t="n">
-        <v>-9.6</v>
+      <c r="F7" t="n">
+        <v>113</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>-9.6</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+      <c r="H7" s="4" t="n">
+        <v>-9.6</v>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1356,33 +1413,36 @@
         <v>125</v>
       </c>
       <c r="D8" t="n">
-        <v>113</v>
+        <v/>
       </c>
       <c r="E8" t="n">
         <v>113</v>
       </c>
-      <c r="F8" s="4" t="n">
-        <v>-9.6</v>
+      <c r="F8" t="n">
+        <v>113</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>-9.6</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+      <c r="H8" s="4" t="n">
+        <v>-9.6</v>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1403,33 +1463,36 @@
         <v>2660</v>
       </c>
       <c r="D9" t="n">
+        <v/>
+      </c>
+      <c r="E9" t="n">
         <v>2550</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>3140</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>18.05</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>-4.14</v>
       </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1450,33 +1513,36 @@
         <v>260</v>
       </c>
       <c r="D10" t="n">
-        <v>286</v>
+        <v/>
       </c>
       <c r="E10" t="n">
         <v>286</v>
       </c>
-      <c r="F10" s="4" t="n">
-        <v>10</v>
+      <c r="F10" t="n">
+        <v>286</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H10" s="4" t="n">
+        <v>10</v>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1497,33 +1563,36 @@
         <v>109</v>
       </c>
       <c r="D11" t="n">
+        <v/>
+      </c>
+      <c r="E11" t="n">
         <v>101</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>106</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>-2.75</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>-7.34</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1544,33 +1613,36 @@
         <v>740</v>
       </c>
       <c r="D12" t="n">
+        <v/>
+      </c>
+      <c r="E12" t="n">
         <v>735</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>750</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>1.35</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>-0.68</v>
       </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1591,33 +1663,36 @@
         <v>4050</v>
       </c>
       <c r="D13" t="n">
-        <v>4400</v>
+        <v/>
       </c>
       <c r="E13" t="n">
         <v>4400</v>
       </c>
-      <c r="F13" s="4" t="n">
-        <v>8.640000000000001</v>
+      <c r="F13" t="n">
+        <v>4400</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>8.640000000000001</v>
       </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H13" s="4" t="n">
+        <v>8.640000000000001</v>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1638,33 +1713,36 @@
         <v>328</v>
       </c>
       <c r="D14" t="n">
+        <v/>
+      </c>
+      <c r="E14" t="n">
         <v>320</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>328</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>-2.44</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1685,33 +1763,36 @@
         <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v/>
       </c>
       <c r="E15" t="n">
         <v>82</v>
       </c>
-      <c r="F15" s="4" t="n">
-        <v>2.5</v>
+      <c r="F15" t="n">
+        <v>82</v>
       </c>
       <c r="G15" s="4" t="n">
         <v>2.5</v>
       </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H15" s="4" t="n">
+        <v>2.5</v>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1732,33 +1813,36 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
+        <v/>
+      </c>
+      <c r="E16" t="n">
         <v>108</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>117</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>4.46</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="H16" s="4" t="n">
         <v>-3.57</v>
       </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1779,33 +1863,36 @@
         <v>780</v>
       </c>
       <c r="D17" t="n">
+        <v/>
+      </c>
+      <c r="E17" t="n">
         <v>765</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>790</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="G17" s="4" t="n">
         <v>1.28</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="H17" s="4" t="n">
         <v>-1.92</v>
       </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1826,33 +1913,36 @@
         <v>1700</v>
       </c>
       <c r="D18" t="n">
+        <v/>
+      </c>
+      <c r="E18" t="n">
         <v>1690</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>1710</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>0.59</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="H18" s="4" t="n">
         <v>-0.59</v>
       </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1873,33 +1963,36 @@
         <v>625</v>
       </c>
       <c r="D19" t="n">
+        <v/>
+      </c>
+      <c r="E19" t="n">
         <v>590</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>625</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="G19" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="H19" s="4" t="n">
         <v>-5.6</v>
       </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1920,33 +2013,36 @@
         <v>1610</v>
       </c>
       <c r="D20" t="n">
+        <v/>
+      </c>
+      <c r="E20" t="n">
         <v>1585</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>1600</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="G20" s="4" t="n">
         <v>-0.62</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="H20" s="4" t="n">
         <v>-1.55</v>
       </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1967,33 +2063,36 @@
         <v>2820</v>
       </c>
       <c r="D21" t="n">
+        <v/>
+      </c>
+      <c r="E21" t="n">
         <v>3080</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>3290</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="G21" s="4" t="n">
         <v>16.67</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="H21" s="4" t="n">
         <v>9.220000000000001</v>
       </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2014,33 +2113,36 @@
         <v>242</v>
       </c>
       <c r="D22" t="n">
+        <v/>
+      </c>
+      <c r="E22" t="n">
         <v>234</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>246</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="G22" s="4" t="n">
         <v>1.65</v>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="H22" s="4" t="n">
         <v>-3.31</v>
       </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2061,33 +2163,36 @@
         <v>81</v>
       </c>
       <c r="D23" t="n">
+        <v/>
+      </c>
+      <c r="E23" t="n">
         <v>75</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>87</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="G23" s="4" t="n">
         <v>7.41</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="H23" s="4" t="n">
         <v>-7.41</v>
       </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2108,33 +2213,36 @@
         <v>620</v>
       </c>
       <c r="D24" t="n">
+        <v/>
+      </c>
+      <c r="E24" t="n">
         <v>605</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>625</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="G24" s="4" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="H24" s="4" t="n">
         <v>-2.42</v>
       </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2155,33 +2263,36 @@
         <v>418</v>
       </c>
       <c r="D25" t="n">
+        <v/>
+      </c>
+      <c r="E25" t="n">
         <v>390</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>440</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="G25" s="4" t="n">
         <v>5.26</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="H25" s="4" t="n">
         <v>-6.7</v>
       </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2202,33 +2313,36 @@
         <v>9150</v>
       </c>
       <c r="D26" t="n">
+        <v/>
+      </c>
+      <c r="E26" t="n">
         <v>8700</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>9150</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="G26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="H26" s="4" t="n">
         <v>-4.92</v>
       </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2249,33 +2363,36 @@
         <v>396</v>
       </c>
       <c r="D27" t="n">
+        <v/>
+      </c>
+      <c r="E27" t="n">
         <v>372</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>396</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="G27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="H27" s="4" t="n">
         <v>-6.06</v>
       </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2296,33 +2413,36 @@
         <v>81</v>
       </c>
       <c r="D28" t="n">
+        <v/>
+      </c>
+      <c r="E28" t="n">
         <v>69</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>85</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="G28" s="4" t="n">
         <v>4.94</v>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="H28" s="4" t="n">
         <v>-14.81</v>
       </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2343,33 +2463,36 @@
         <v>218</v>
       </c>
       <c r="D29" t="n">
+        <v/>
+      </c>
+      <c r="E29" t="n">
         <v>186</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>208</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="G29" s="4" t="n">
         <v>-4.59</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="H29" s="4" t="n">
         <v>-14.68</v>
       </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2390,33 +2513,36 @@
         <v>117</v>
       </c>
       <c r="D30" t="n">
+        <v/>
+      </c>
+      <c r="E30" t="n">
         <v>120</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>127</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="G30" s="4" t="n">
         <v>8.550000000000001</v>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="H30" s="4" t="n">
         <v>2.56</v>
       </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2437,33 +2563,36 @@
         <v>640</v>
       </c>
       <c r="D31" t="n">
+        <v/>
+      </c>
+      <c r="E31" t="n">
         <v>585</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>640</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="G31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="H31" s="4" t="n">
         <v>-8.59</v>
       </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2484,33 +2613,36 @@
         <v>282</v>
       </c>
       <c r="D32" t="n">
-        <v>284</v>
+        <v/>
       </c>
       <c r="E32" t="n">
         <v>284</v>
       </c>
-      <c r="F32" s="4" t="n">
-        <v>0.71</v>
+      <c r="F32" t="n">
+        <v>284</v>
       </c>
       <c r="G32" s="4" t="n">
         <v>0.71</v>
       </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H32" s="4" t="n">
+        <v>0.71</v>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2531,33 +2663,36 @@
         <v>264</v>
       </c>
       <c r="D33" t="n">
+        <v/>
+      </c>
+      <c r="E33" t="n">
         <v>286</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>290</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="G33" s="4" t="n">
         <v>9.85</v>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="H33" s="4" t="n">
         <v>8.33</v>
       </c>
-      <c r="H33" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2578,33 +2713,36 @@
         <v>98</v>
       </c>
       <c r="D34" t="n">
-        <v>101</v>
+        <v/>
       </c>
       <c r="E34" t="n">
         <v>101</v>
       </c>
-      <c r="F34" s="4" t="n">
-        <v>3.06</v>
+      <c r="F34" t="n">
+        <v>101</v>
       </c>
       <c r="G34" s="4" t="n">
         <v>3.06</v>
       </c>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H34" s="4" t="n">
+        <v>3.06</v>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2625,33 +2763,36 @@
         <v>98</v>
       </c>
       <c r="D35" t="n">
+        <v/>
+      </c>
+      <c r="E35" t="n">
         <v>94</v>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>100</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="G35" s="4" t="n">
         <v>2.04</v>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="H35" s="4" t="n">
         <v>-4.08</v>
       </c>
-      <c r="H35" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2672,33 +2813,36 @@
         <v>92</v>
       </c>
       <c r="D36" t="n">
+        <v/>
+      </c>
+      <c r="E36" t="n">
         <v>89</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>93</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="G36" s="4" t="n">
         <v>1.09</v>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="H36" s="4" t="n">
         <v>-3.26</v>
       </c>
-      <c r="H36" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2719,33 +2863,36 @@
         <v>89</v>
       </c>
       <c r="D37" t="n">
+        <v/>
+      </c>
+      <c r="E37" t="n">
         <v>81</v>
       </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
         <v>91</v>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="G37" s="4" t="n">
         <v>2.25</v>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="H37" s="4" t="n">
         <v>-8.99</v>
       </c>
-      <c r="H37" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2766,33 +2913,36 @@
         <v>90</v>
       </c>
       <c r="D38" t="n">
+        <v/>
+      </c>
+      <c r="E38" t="n">
         <v>82</v>
       </c>
-      <c r="E38" t="n">
+      <c r="F38" t="n">
         <v>112</v>
       </c>
-      <c r="F38" s="4" t="n">
+      <c r="G38" s="4" t="n">
         <v>24.44</v>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="H38" s="4" t="n">
         <v>-8.890000000000001</v>
       </c>
-      <c r="H38" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I38" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2813,33 +2963,36 @@
         <v>60</v>
       </c>
       <c r="D39" t="n">
+        <v/>
+      </c>
+      <c r="E39" t="n">
         <v>57</v>
       </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
         <v>61</v>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="G39" s="4" t="n">
         <v>1.67</v>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="H39" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="H39" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I39" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2860,33 +3013,36 @@
         <v>138</v>
       </c>
       <c r="D40" t="n">
+        <v/>
+      </c>
+      <c r="E40" t="n">
         <v>176</v>
       </c>
-      <c r="E40" t="n">
+      <c r="F40" t="n">
         <v>181</v>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="G40" s="4" t="n">
         <v>31.16</v>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="H40" s="4" t="n">
         <v>27.54</v>
       </c>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2907,33 +3063,36 @@
         <v>360</v>
       </c>
       <c r="D41" t="n">
+        <v/>
+      </c>
+      <c r="E41" t="n">
         <v>362</v>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>432</v>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="G41" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="H41" s="4" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="H41" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2954,33 +3113,36 @@
         <v>151</v>
       </c>
       <c r="D42" t="n">
+        <v/>
+      </c>
+      <c r="E42" t="n">
         <v>160</v>
       </c>
-      <c r="E42" t="n">
+      <c r="F42" t="n">
         <v>169</v>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="G42" s="4" t="n">
         <v>11.92</v>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="H42" s="4" t="n">
         <v>5.96</v>
       </c>
-      <c r="H42" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>

--- a/data/performance/daily/signal_list_2026-06-30.xlsx
+++ b/data/performance/daily/signal_list_2026-06-30.xlsx
@@ -559,7 +559,7 @@
         <v>125</v>
       </c>
       <c r="D5" t="n">
-        <v/>
+        <v>113</v>
       </c>
       <c r="E5" t="n">
         <v>113</v>
@@ -609,7 +609,7 @@
         <v>125</v>
       </c>
       <c r="D6" t="n">
-        <v/>
+        <v>113</v>
       </c>
       <c r="E6" t="n">
         <v>113</v>
@@ -659,7 +659,7 @@
         <v>125</v>
       </c>
       <c r="D7" t="n">
-        <v/>
+        <v>113</v>
       </c>
       <c r="E7" t="n">
         <v>113</v>
@@ -709,7 +709,7 @@
         <v>125</v>
       </c>
       <c r="D8" t="n">
-        <v/>
+        <v>113</v>
       </c>
       <c r="E8" t="n">
         <v>113</v>
@@ -759,7 +759,7 @@
         <v>3980</v>
       </c>
       <c r="D9" t="n">
-        <v/>
+        <v>3980</v>
       </c>
       <c r="E9" t="n">
         <v>3960</v>
@@ -809,7 +809,7 @@
         <v>328</v>
       </c>
       <c r="D10" t="n">
-        <v/>
+        <v>328</v>
       </c>
       <c r="E10" t="n">
         <v>320</v>
@@ -859,7 +859,7 @@
         <v>16475</v>
       </c>
       <c r="D11" t="n">
-        <v/>
+        <v>15675</v>
       </c>
       <c r="E11" t="n">
         <v>16250</v>
@@ -909,7 +909,7 @@
         <v>1080</v>
       </c>
       <c r="D12" t="n">
-        <v/>
+        <v>1080</v>
       </c>
       <c r="E12" t="n">
         <v>1080</v>
@@ -959,7 +959,7 @@
         <v>1510</v>
       </c>
       <c r="D13" t="n">
-        <v/>
+        <v>1505.03</v>
       </c>
       <c r="E13" t="n">
         <v>1525</v>
@@ -1009,7 +1009,7 @@
         <v>960</v>
       </c>
       <c r="D14" t="n">
-        <v/>
+        <v>965</v>
       </c>
       <c r="E14" t="n">
         <v>945</v>
@@ -1059,7 +1059,7 @@
         <v>98</v>
       </c>
       <c r="D15" t="n">
-        <v/>
+        <v>98</v>
       </c>
       <c r="E15" t="n">
         <v>94</v>
@@ -1109,7 +1109,7 @@
         <v>1220</v>
       </c>
       <c r="D16" t="n">
-        <v/>
+        <v>1209.81</v>
       </c>
       <c r="E16" t="n">
         <v>1170</v>
@@ -1263,7 +1263,7 @@
         <v>125</v>
       </c>
       <c r="D5" t="n">
-        <v/>
+        <v>113</v>
       </c>
       <c r="E5" t="n">
         <v>113</v>
@@ -1313,7 +1313,7 @@
         <v>125</v>
       </c>
       <c r="D6" t="n">
-        <v/>
+        <v>113</v>
       </c>
       <c r="E6" t="n">
         <v>113</v>
@@ -1363,7 +1363,7 @@
         <v>125</v>
       </c>
       <c r="D7" t="n">
-        <v/>
+        <v>113</v>
       </c>
       <c r="E7" t="n">
         <v>113</v>
@@ -1413,7 +1413,7 @@
         <v>125</v>
       </c>
       <c r="D8" t="n">
-        <v/>
+        <v>113</v>
       </c>
       <c r="E8" t="n">
         <v>113</v>
@@ -1463,7 +1463,7 @@
         <v>2660</v>
       </c>
       <c r="D9" t="n">
-        <v/>
+        <v>2700</v>
       </c>
       <c r="E9" t="n">
         <v>2550</v>
@@ -1513,7 +1513,7 @@
         <v>260</v>
       </c>
       <c r="D10" t="n">
-        <v/>
+        <v>260</v>
       </c>
       <c r="E10" t="n">
         <v>286</v>
@@ -1563,7 +1563,7 @@
         <v>109</v>
       </c>
       <c r="D11" t="n">
-        <v/>
+        <v>106</v>
       </c>
       <c r="E11" t="n">
         <v>101</v>
@@ -1613,7 +1613,7 @@
         <v>740</v>
       </c>
       <c r="D12" t="n">
-        <v/>
+        <v>735</v>
       </c>
       <c r="E12" t="n">
         <v>735</v>
@@ -1663,7 +1663,7 @@
         <v>4050</v>
       </c>
       <c r="D13" t="n">
-        <v/>
+        <v>3890</v>
       </c>
       <c r="E13" t="n">
         <v>4400</v>
@@ -1713,7 +1713,7 @@
         <v>328</v>
       </c>
       <c r="D14" t="n">
-        <v/>
+        <v>328</v>
       </c>
       <c r="E14" t="n">
         <v>320</v>
@@ -1763,7 +1763,7 @@
         <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v/>
+        <v>80</v>
       </c>
       <c r="E15" t="n">
         <v>82</v>
@@ -1813,7 +1813,7 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v/>
+        <v>112</v>
       </c>
       <c r="E16" t="n">
         <v>108</v>
@@ -1863,7 +1863,7 @@
         <v>780</v>
       </c>
       <c r="D17" t="n">
-        <v/>
+        <v>785</v>
       </c>
       <c r="E17" t="n">
         <v>765</v>
@@ -1913,7 +1913,7 @@
         <v>1700</v>
       </c>
       <c r="D18" t="n">
-        <v/>
+        <v>1700</v>
       </c>
       <c r="E18" t="n">
         <v>1690</v>
@@ -1963,7 +1963,7 @@
         <v>625</v>
       </c>
       <c r="D19" t="n">
-        <v/>
+        <v>625</v>
       </c>
       <c r="E19" t="n">
         <v>590</v>
@@ -2013,7 +2013,7 @@
         <v>1610</v>
       </c>
       <c r="D20" t="n">
-        <v/>
+        <v>1600</v>
       </c>
       <c r="E20" t="n">
         <v>1585</v>
@@ -2063,7 +2063,7 @@
         <v>2820</v>
       </c>
       <c r="D21" t="n">
-        <v/>
+        <v>2820</v>
       </c>
       <c r="E21" t="n">
         <v>3080</v>
@@ -2113,7 +2113,7 @@
         <v>242</v>
       </c>
       <c r="D22" t="n">
-        <v/>
+        <v>240</v>
       </c>
       <c r="E22" t="n">
         <v>234</v>
@@ -2163,7 +2163,7 @@
         <v>81</v>
       </c>
       <c r="D23" t="n">
-        <v/>
+        <v>84</v>
       </c>
       <c r="E23" t="n">
         <v>75</v>
@@ -2213,7 +2213,7 @@
         <v>620</v>
       </c>
       <c r="D24" t="n">
-        <v/>
+        <v>620</v>
       </c>
       <c r="E24" t="n">
         <v>605</v>
@@ -2263,7 +2263,7 @@
         <v>418</v>
       </c>
       <c r="D25" t="n">
-        <v/>
+        <v>396.36</v>
       </c>
       <c r="E25" t="n">
         <v>390</v>
@@ -2313,7 +2313,7 @@
         <v>9150</v>
       </c>
       <c r="D26" t="n">
-        <v/>
+        <v>9150</v>
       </c>
       <c r="E26" t="n">
         <v>8700</v>
@@ -2363,7 +2363,7 @@
         <v>396</v>
       </c>
       <c r="D27" t="n">
-        <v/>
+        <v>396</v>
       </c>
       <c r="E27" t="n">
         <v>372</v>
@@ -2413,7 +2413,7 @@
         <v>81</v>
       </c>
       <c r="D28" t="n">
-        <v/>
+        <v>81</v>
       </c>
       <c r="E28" t="n">
         <v>69</v>
@@ -2463,7 +2463,7 @@
         <v>218</v>
       </c>
       <c r="D29" t="n">
-        <v/>
+        <v>202</v>
       </c>
       <c r="E29" t="n">
         <v>186</v>
@@ -2513,7 +2513,7 @@
         <v>117</v>
       </c>
       <c r="D30" t="n">
-        <v/>
+        <v>124</v>
       </c>
       <c r="E30" t="n">
         <v>120</v>
@@ -2563,7 +2563,7 @@
         <v>640</v>
       </c>
       <c r="D31" t="n">
-        <v/>
+        <v>635</v>
       </c>
       <c r="E31" t="n">
         <v>585</v>
@@ -2613,7 +2613,7 @@
         <v>282</v>
       </c>
       <c r="D32" t="n">
-        <v/>
+        <v>282</v>
       </c>
       <c r="E32" t="n">
         <v>284</v>
@@ -2663,7 +2663,7 @@
         <v>264</v>
       </c>
       <c r="D33" t="n">
-        <v/>
+        <v>264</v>
       </c>
       <c r="E33" t="n">
         <v>286</v>
@@ -2713,7 +2713,7 @@
         <v>98</v>
       </c>
       <c r="D34" t="n">
-        <v/>
+        <v>100</v>
       </c>
       <c r="E34" t="n">
         <v>101</v>
@@ -2763,7 +2763,7 @@
         <v>98</v>
       </c>
       <c r="D35" t="n">
-        <v/>
+        <v>98</v>
       </c>
       <c r="E35" t="n">
         <v>94</v>
@@ -2813,7 +2813,7 @@
         <v>92</v>
       </c>
       <c r="D36" t="n">
-        <v/>
+        <v>91</v>
       </c>
       <c r="E36" t="n">
         <v>89</v>
@@ -2863,7 +2863,7 @@
         <v>89</v>
       </c>
       <c r="D37" t="n">
-        <v/>
+        <v>89</v>
       </c>
       <c r="E37" t="n">
         <v>81</v>
@@ -2913,7 +2913,7 @@
         <v>90</v>
       </c>
       <c r="D38" t="n">
-        <v/>
+        <v>91</v>
       </c>
       <c r="E38" t="n">
         <v>82</v>
@@ -2963,7 +2963,7 @@
         <v>60</v>
       </c>
       <c r="D39" t="n">
-        <v/>
+        <v>60</v>
       </c>
       <c r="E39" t="n">
         <v>57</v>
@@ -3013,7 +3013,7 @@
         <v>138</v>
       </c>
       <c r="D40" t="n">
-        <v/>
+        <v>143</v>
       </c>
       <c r="E40" t="n">
         <v>176</v>
@@ -3063,7 +3063,7 @@
         <v>360</v>
       </c>
       <c r="D41" t="n">
-        <v/>
+        <v>406</v>
       </c>
       <c r="E41" t="n">
         <v>362</v>
@@ -3113,7 +3113,7 @@
         <v>151</v>
       </c>
       <c r="D42" t="n">
-        <v/>
+        <v>151</v>
       </c>
       <c r="E42" t="n">
         <v>160</v>
